--- a/database_penyimpanan_aman/arsip_dokumen_customer/metadata_arsip.xlsx
+++ b/database_penyimpanan_aman/arsip_dokumen_customer/metadata_arsip.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,14 +462,24 @@
           <t>Nomor Kontrak</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Nomor PI</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Nomor PO / Ref</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 13:12</t>
+          <t>2026-09-15 10:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -480,12 +490,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PO_No_4500011581_Pembelian_Baricade_line_1.pdf</t>
+          <t>PO_No_4500011581_Pembelian_Baricade_line.pdf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011581_Pembelian_Baricade_line_1.pdf</t>
+          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011581_Pembelian_Baricade_line.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -493,364 +503,60 @@
           <t>Baricade / Police line untuk lokasi senoro + Kabel 2 x 1,5 untuk Senoro</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>7201250141</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>001/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>4500011581</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 13:24</t>
+          <t>2026-09-15 10:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PO (Purchase Order) Customer</t>
+          <t>Proforma Invoice (PI)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PO_No_4500011203_Material_pembuatan_grouting_annulus_SNR-19._1.pdf</t>
+          <t>PI_No_001_BSS-JOB_WS_I_2026_Pengadaan_material_dan_Safety_Equipment_Kosong.pdf</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011203_Material_pembuatan_grouting_annulus_SNR-19._1.pdf</t>
+          <t>database_penyimpanan_aman\arsip_dokumen_customer\02_Proforma_Invoice\PI_No_001_BSS-JOB_WS_I_2026_Pengadaan_material_dan_Safety_Equipment_Kosong.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
-        </is>
-      </c>
+          <t>Baricade / Police line untuk lokasi senoro + Kabel 2 x 1,5 untuk Senoro</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>7201250141</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:26</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PO_No._4500011236_-_Pengiriman_OCTG_Cilegon_-_Senoro_rev2_1.pdf</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No._4500011236_-_Pengiriman_OCTG_Cilegon_-_Senoro_rev2_1.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>004BSS-JOB/WS/II/2026</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PO_No_4500011579_Pembelian_Ban_Lighting_tower_1.pdf</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011579_Pembelian_Ban_Lighting_tower_1.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>(Provisional Sum) Penyediaan Ban Sparepart Genset Field Maintenance</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:37</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PO_No_4500011580_sewa_mobil_pengiriman_lampu_lghting_tower_1.pdf</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011580_sewa_mobil_pengiriman_lampu_lghting_tower_1.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Transport Pengangkutan Material Sparepart Genset Field Maintenance</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:40</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PO_No_4500011681_Kendaraan_untuk_support_crew_JOB.pdf</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011681_Kendaraan_untuk_support_crew_JOB.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Sewa Mobil team JOB Kegiatan Inspeksi Equipment periode 6 sd 9 Jui 2026</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:49</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PO_No_4500011586_Provsum_Hotel_untuk_Meeting.pdf</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011586_Provsum_Hotel_untuk_Meeting.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Provsum pembayaran Hotel Artotel Acara meeting HSE, pembayaran tgl 5 Agustus 2026</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:51</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PO_No_4500011682_Material_Kabel.pdf</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011682_Material_Kabel.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>(Provsum) Pengadaan Material Kabel Pendukung Kegiatan SBHP di Cluster SNR 2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:51</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PO (Purchase Order) Customer</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PO_No_4500011683_Kendaraan_Pengiriman_Kabel.pdf</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011683_Kendaraan_Pengiriman_Kabel.pdf</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Transportasi untuk Pengangkutan Material Kabel Pendukung Kegiatan SBHP di Cluster SNR 2</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>018/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7201250141</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-09 14:06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Proforma Invoice (PI)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PI_NO_017-BSS-JOB-WS-VIII-2026_Pengadaan_Material_Kabel.pdf</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>database_penyimpanan_aman\arsip_dokumen_customer\02_Proforma_Invoice\PI_NO_017-BSS-JOB-WS-VIII-2026_Pengadaan_Material_Kabel.pdf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>(Provsum) Pengadaan Material Kabel Pendukung Kegiatan SBHP di Cluster SNR 2</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>7201250141</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>001/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>4500011581</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/arsip_dokumen_customer/metadata_arsip.xlsx
+++ b/database_penyimpanan_aman/arsip_dokumen_customer/metadata_arsip.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,49 @@
       </c>
       <c r="K3" t="n">
         <v>4500011581</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-20 06:38</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PO (Purchase Order) Customer</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PO_No_4500011739_Supporting_equipment_kegiatan_well_services_2026_periode_PO_03_agustus_sd_30_November_2026.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011739_Supporting_equipment_kegiatan_well_services_2026_periode_PO_03_agustus_sd_30_November_2026.pdf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan well services 2026 periode PO 03 agustus sd 30 November 2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>4500011739</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/arsip_dokumen_customer/metadata_arsip.xlsx
+++ b/database_penyimpanan_aman/arsip_dokumen_customer/metadata_arsip.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,49 @@
       </c>
       <c r="K4" t="n">
         <v>4500011739</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:39</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PO (Purchase Order) Customer</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PO_No_4500011580_sewa_mobil_pengiriman_lampu_lghting_tower.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>database_penyimpanan_aman\arsip_dokumen_customer\01_Purchase_Order\PO_No_4500011580_sewa_mobil_pengiriman_lampu_lghting_tower.pdf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sewa mobil pengiriman lampu lghting tower</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4500011580</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>4500011580</v>
       </c>
     </row>
   </sheetData>
